--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/_event.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/_event.xlsx
@@ -1010,8 +1010,8 @@
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>"... A espada," "Minha espada..."
-Ha! Ha! Ha! Que lamentações deploráveis!</t>
+          <t>"...A espada," "Minha espada..."
+Ha! Ha! Ha! Que lamentações lastimáveis!</t>
         </is>
       </c>
       <c r="L30" s="12" t="n"/>
@@ -1282,8 +1282,8 @@
       <c r="K31" t="inlineStr">
         <is>
           <t>Meros mortais,
-Não, insetos insignificantes,
-Suas espadas me servirão eternamente.</t>
+não, insetos insignificantes,
+suas espadas servirão a mim eternamente.</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Então, você é o tolo que ousa levantar uma lâmina contra um deus?</t>
+          <t>Então você é o tolo que ousa erguer uma lâmina contra um deus?</t>
         </is>
       </c>
     </row>
@@ -1682,9 +1682,9 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Eu estava observando, a todo momento.
-Os gritos lamentáveis das almas libertadas
-eram uma melodia deliciosa para meus ouvidos.</t>
+          <t>Estive assistindo, cada instante.
+Os choros lastimáveis das almas libertadas
+Eram uma melodia deliciosa aos meus ouvidos.</t>
         </is>
       </c>
     </row>
@@ -1706,8 +1706,8 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Muito bem, inseto, vou te agradar._x000D_
-Dance com esta espada!</t>
+          <t>Muito bem, inseto, vou te dar atenção.
+Dança com esta espada!</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>O quê? Derrotado por meros insetos?</t>
+          <t>O-o quê? Derrotado por meros insetos?</t>
         </is>
       </c>
       <c r="L52" s="12" t="n"/>
@@ -2308,8 +2308,8 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Lembre-se disso, mortal._x000D_
-Eu certamente retornarei para tomar de volta aquela espada!</t>
+          <t>Guarde isto, mortal.
+Certamente voltarei para tomar de volta aquela espada!</t>
         </is>
       </c>
     </row>
